--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:07</t>
+    <t xml:space="preserve">2026-09-09 23:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:01</t>
+    <t xml:space="preserve">2026-09-17 13:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:58</t>
+    <t xml:space="preserve">2026-09-23 12:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:27</t>
+    <t xml:space="preserve">2026-10-02 13:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:45</t>
+    <t xml:space="preserve">2026-10-04 08:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:48</t>
+    <t xml:space="preserve">2026-10-05 10:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -626,7 +626,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>885800.12</v>
+        <v>885800.13</v>
       </c>
     </row>
     <row r="5">
@@ -677,7 +677,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>847963.12</v>
+        <v>847963.13</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         <v>2019</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>748045.12</v>
+        <v>748045.13</v>
       </c>
     </row>
     <row r="17">
@@ -932,7 +932,7 @@
         <v>2019</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>698763.62</v>
+        <v>698763.63</v>
       </c>
     </row>
     <row r="23">
@@ -1136,7 +1136,7 @@
         <v>2019</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>640436.12</v>
+        <v>640436.13</v>
       </c>
     </row>
     <row r="35">
